--- a/output/log/fourthVersion/表4_比較法調查估價表_已填.xlsx
+++ b/output/log/fourthVersion/表4_比較法調查估價表_已填.xlsx
@@ -6438,7 +6438,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>產生日期：2026-09-12　產生器：engine/export_xlsx.py</t>
+          <t>產生日期：2026-09-13　產生器：engine/export_xlsx.py</t>
         </is>
       </c>
     </row>
